--- a/ig/test-tabs-svs/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/test-tabs-svs/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -233,12 +233,6 @@
     <t>34875-5</t>
   </si>
   <si>
-    <t>34876-3</t>
-  </si>
-  <si>
-    <t>34895-3</t>
-  </si>
-  <si>
     <t>39256-3</t>
   </si>
   <si>
@@ -272,6 +266,9 @@
     <t>56445-0</t>
   </si>
   <si>
+    <t>55751-2</t>
+  </si>
+  <si>
     <t>56446-8</t>
   </si>
   <si>
@@ -314,21 +311,12 @@
     <t>61357-0</t>
   </si>
   <si>
-    <t>61358-8</t>
-  </si>
-  <si>
-    <t>61359-6</t>
-  </si>
-  <si>
     <t>67851-6</t>
   </si>
   <si>
     <t>68599-0</t>
   </si>
   <si>
-    <t>68814-3</t>
-  </si>
-  <si>
     <t>68817-6</t>
   </si>
   <si>
@@ -401,15 +389,9 @@
     <t>83901-9</t>
   </si>
   <si>
-    <t>83963-9</t>
-  </si>
-  <si>
     <t>83981-1</t>
   </si>
   <si>
-    <t>84067-8</t>
-  </si>
-  <si>
     <t>85208-7</t>
   </si>
   <si>
@@ -443,15 +425,6 @@
     <t>96173-0</t>
   </si>
   <si>
-    <t>97694-4</t>
-  </si>
-  <si>
-    <t>100967-9</t>
-  </si>
-  <si>
-    <t>101881-1</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -465,9 +438,6 @@
   </si>
   <si>
     <t>ATTEST-DROITS-AM</t>
-  </si>
-  <si>
-    <t>ATTEST-VITALE</t>
   </si>
   <si>
     <t>AUTORIS-SOINS</t>
@@ -854,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1316,7 +1286,7 @@
         <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -1342,13 +1312,13 @@
         <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -1361,14 +1331,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1381,7 +1351,7 @@
         <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1394,7 +1364,7 @@
         <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2"/>
     </row>
@@ -1420,7 +1390,7 @@
         <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1433,7 +1403,7 @@
         <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1446,7 +1416,7 @@
         <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1459,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1498,7 +1468,7 @@
         <v>34</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1537,7 +1507,7 @@
         <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1550,7 +1520,7 @@
         <v>34</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1563,7 +1533,7 @@
         <v>34</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1576,7 +1546,7 @@
         <v>34</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1589,7 +1559,7 @@
         <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1602,7 +1572,7 @@
         <v>34</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1615,7 +1585,7 @@
         <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1628,7 +1598,7 @@
         <v>34</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1641,7 +1611,7 @@
         <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1654,7 +1624,7 @@
         <v>34</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -1693,26 +1663,26 @@
         <v>34</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -1725,27 +1695,27 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -1758,7 +1728,7 @@
         <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E69" s="2"/>
     </row>
@@ -1784,7 +1754,7 @@
         <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -1797,7 +1767,7 @@
         <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -1810,7 +1780,7 @@
         <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -1836,7 +1806,7 @@
         <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1849,59 +1819,59 @@
         <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1927,7 +1897,7 @@
         <v>34</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1940,7 +1910,7 @@
         <v>34</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -1953,7 +1923,7 @@
         <v>34</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1966,7 +1936,7 @@
         <v>34</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1979,7 +1949,7 @@
         <v>34</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1992,7 +1962,7 @@
         <v>34</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -2005,7 +1975,7 @@
         <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -2031,7 +2001,7 @@
         <v>34</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2044,7 +2014,7 @@
         <v>34</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2057,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2070,7 +2040,7 @@
         <v>34</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2083,126 +2053,9 @@
         <v>34</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E94" s="2"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B95" s="2"/>
-      <c r="C95" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D95" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B96" s="2"/>
-      <c r="C96" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="B97" s="2"/>
-      <c r="C97" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B98" s="2"/>
-      <c r="C98" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D98" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B99" s="2"/>
-      <c r="C99" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D99" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B100" s="2"/>
-      <c r="C100" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D100" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="B101" s="2"/>
-      <c r="C101" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D101" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B102" s="2"/>
-      <c r="C102" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D102" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B103" s="2"/>
-      <c r="C103" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D103" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E103" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2211,7 +2064,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2233,7 +2086,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2250,241 +2103,241 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2497,150 +2350,150 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>53</v>
+        <v>163</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2653,7 +2506,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2666,7 +2519,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2679,7 +2532,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2692,7 +2545,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2705,42 +2558,29 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="E39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E40" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2771,7 +2611,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2780,7 +2620,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2788,14 +2628,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2"/>
     </row>
